--- a/VaydeerMacropadTemplate.xlsx
+++ b/VaydeerMacropadTemplate.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$10</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>C+5</t>
   </si>
@@ -49,89 +52,59 @@
     <t>C+B</t>
   </si>
   <si>
-    <t>S+F5</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
     <t>JS Run</t>
   </si>
   <si>
     <t>F8</t>
   </si>
   <si>
-    <t>F10</t>
-  </si>
-  <si>
-    <t>Run Dbg</t>
-  </si>
-  <si>
-    <t>Stop Dbg</t>
-  </si>
-  <si>
-    <t>Debug Test</t>
-  </si>
-  <si>
-    <t>Run Teset</t>
-  </si>
-  <si>
     <t>Dbg Over</t>
   </si>
   <si>
     <t>Dbg Into</t>
   </si>
   <si>
-    <t>F11</t>
-  </si>
-  <si>
-    <t>Mic Toggle</t>
-  </si>
-  <si>
-    <t>Share Scrn</t>
-  </si>
-  <si>
-    <t>C+E</t>
-  </si>
-  <si>
-    <t>End Mtg</t>
-  </si>
-  <si>
-    <t>C+H</t>
-  </si>
-  <si>
-    <t>VS</t>
-  </si>
-  <si>
-    <t>Win+3</t>
-  </si>
-  <si>
-    <t>SqlEd</t>
-  </si>
-  <si>
-    <t>Win+4</t>
-  </si>
-  <si>
-    <t>C+S+K</t>
-  </si>
-  <si>
-    <t>TeamsClap</t>
-  </si>
-  <si>
-    <t>TypeAdmin</t>
-  </si>
-  <si>
-    <t>AdminPwd</t>
-  </si>
-  <si>
-    <t>CorpPwd</t>
+    <t>Close Win</t>
+  </si>
+  <si>
+    <t>Type Admin</t>
+  </si>
+  <si>
+    <t>Run Test</t>
+  </si>
+  <si>
+    <t>Dbg Test</t>
+  </si>
+  <si>
+    <t>Type Admin Pwd</t>
+  </si>
+  <si>
+    <t>Type Dev Supp Pwd</t>
+  </si>
+  <si>
+    <t>Type My Pwd</t>
+  </si>
+  <si>
+    <t>S+F9</t>
+  </si>
+  <si>
+    <t>DbgQckWtch</t>
+  </si>
+  <si>
+    <t>VS VM</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>ExitApp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +121,25 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -173,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -362,11 +354,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -443,6 +474,54 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,7 +726,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>4601</xdr:colOff>
+      <xdr:colOff>4602</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>457200</xdr:rowOff>
     </xdr:to>
@@ -997,10 +1076,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="47.28515625" customWidth="1"/>
+    <col min="4" max="4" width="42.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1032,34 +1111,38 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>29</v>
+        <v>4</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="B4" s="6" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="17"/>
+        <v>15</v>
+      </c>
+      <c r="E4" s="37"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -1082,44 +1165,28 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>23</v>
-      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="28"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>4</v>
-      </c>
+      <c r="A7" s="11"/>
       <c r="B7" s="12" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>24</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E7" s="40"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1143,45 +1210,48 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>16</v>
+      <c r="F9" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="24" t="s">
-        <v>20</v>
-      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="32"/>
     </row>
+    <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+  </mergeCells>
   <pageMargins left="0.25" right="0" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/VaydeerMacropadTemplate.xlsx
+++ b/VaydeerMacropadTemplate.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>C+5</t>
   </si>
@@ -98,6 +98,18 @@
   </si>
   <si>
     <t>ExitApp</t>
+  </si>
+  <si>
+    <t>CloseWin</t>
+  </si>
+  <si>
+    <t>C+F4</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>F11</t>
   </si>
 </sst>
 </file>
@@ -474,6 +486,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -518,9 +533,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,7 +571,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F260F60A-DBEE-42CC-E5BD-D375680FC416}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F260F60A-DBEE-42CC-E5BD-D375680FC416}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -615,7 +627,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA941E0-F4D6-44EA-A8EB-038D50ADF789}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CAA941E0-F4D6-44EA-A8EB-038D50ADF789}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -676,7 +688,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4084323D-88F2-C9F4-2F3F-73A644E97D5D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4084323D-88F2-C9F4-2F3F-73A644E97D5D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -735,7 +747,7 @@
         <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE68B881-E2EA-5CFF-A934-57CD65EC15DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EE68B881-E2EA-5CFF-A934-57CD65EC15DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1117,16 +1129,16 @@
       <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="31" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1140,9 +1152,9 @@
       <c r="C4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="29"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -1165,28 +1177,32 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
+      <c r="A6" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="28"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
+      <c r="A7" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="B7" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="29"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="30"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1218,13 +1234,13 @@
       <c r="C9" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="32" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1232,11 +1248,15 @@
       <c r="A10" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="32"/>
+      <c r="B10" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="33"/>
     </row>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/VaydeerMacropadTemplate.xlsx
+++ b/VaydeerMacropadTemplate.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>C+5</t>
   </si>
@@ -58,75 +58,41 @@
     <t>F8</t>
   </si>
   <si>
-    <t>Dbg Over</t>
-  </si>
-  <si>
-    <t>Dbg Into</t>
-  </si>
-  <si>
     <t>Close Win</t>
   </si>
   <si>
-    <t>Type Admin</t>
-  </si>
-  <si>
     <t>Run Test</t>
   </si>
   <si>
     <t>Dbg Test</t>
   </si>
   <si>
-    <t>Type Admin Pwd</t>
-  </si>
-  <si>
-    <t>Type Dev Supp Pwd</t>
-  </si>
-  <si>
-    <t>Type My Pwd</t>
-  </si>
-  <si>
-    <t>S+F9</t>
-  </si>
-  <si>
-    <t>DbgQckWtch</t>
-  </si>
-  <si>
-    <t>VS VM</t>
-  </si>
-  <si>
-    <t>F12</t>
-  </si>
-  <si>
     <t>ExitApp</t>
   </si>
   <si>
-    <t>CloseWin</t>
-  </si>
-  <si>
-    <t>C+F4</t>
-  </si>
-  <si>
-    <t>F10</t>
-  </si>
-  <si>
-    <t>F11</t>
+    <t>Temp</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Zeerka</t>
+  </si>
+  <si>
+    <t>VSCode</t>
+  </si>
+  <si>
+    <t>Calc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -151,7 +117,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -409,130 +376,133 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,7 +541,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F260F60A-DBEE-42CC-E5BD-D375680FC416}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F260F60A-DBEE-42CC-E5BD-D375680FC416}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -627,7 +597,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CAA941E0-F4D6-44EA-A8EB-038D50ADF789}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA941E0-F4D6-44EA-A8EB-038D50ADF789}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -673,54 +643,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>34428</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>68856</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>408464</xdr:colOff>
+      <xdr:colOff>510745</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>457200</xdr:rowOff>
+      <xdr:rowOff>545173</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4084323D-88F2-C9F4-2F3F-73A644E97D5D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
-              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a14:imgLayer r:embed="rId3">
-                  <a14:imgEffect>
-                    <a14:brightnessContrast bright="40000"/>
-                  </a14:imgEffect>
-                </a14:imgLayer>
-              </a14:imgProps>
-            </a:ext>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1" y="0"/>
-          <a:ext cx="408463" cy="457200"/>
+          <a:off x="34428" y="68856"/>
+          <a:ext cx="476317" cy="476317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -732,54 +681,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>235257</xdr:colOff>
+      <xdr:colOff>77011</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>64851</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>4602</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>579608</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>457200</xdr:rowOff>
+      <xdr:rowOff>561004</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EE68B881-E2EA-5CFF-A934-57CD65EC15DB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="8" name="Picture 7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
-              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a14:imgLayer r:embed="rId5">
-                  <a14:imgEffect>
-                    <a14:brightnessContrast bright="40000"/>
-                  </a14:imgEffect>
-                </a14:imgLayer>
-              </a14:imgProps>
-            </a:ext>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3941974" y="0"/>
-          <a:ext cx="377567" cy="457200"/>
+          <a:off x="3441160" y="64851"/>
+          <a:ext cx="502597" cy="496153"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1091,172 +1019,155 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="42.5703125" customWidth="1"/>
+    <col min="4" max="4" width="4.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25"/>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="27"/>
+      <c r="A1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="32">
         <v>7</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="33">
         <v>8</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="34">
         <v>9</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="32">
         <v>7</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="33">
         <v>8</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="34">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="34" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="31" t="s">
-        <v>13</v>
-      </c>
+      <c r="C3" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="23"/>
+      <c r="G3" s="19"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="30"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="37">
         <v>4</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="36">
         <v>5</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="35">
         <v>6</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="37">
         <v>4</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="36">
         <v>5</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="35">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="E6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="29"/>
+      <c r="F6" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="30"/>
+      <c r="A7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A8" s="38">
         <v>1</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="39">
         <v>2</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="40">
         <v>3</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="38">
         <v>1</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="39">
         <v>2</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="40">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="8"/>
+      <c r="E9" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="20" t="s">
         <v>9</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="35"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="33"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/VaydeerMacropadTemplate.xlsx
+++ b/VaydeerMacropadTemplate.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>C+5</t>
   </si>
@@ -83,6 +83,18 @@
   </si>
   <si>
     <t>Calc</t>
+  </si>
+  <si>
+    <t>MinWin</t>
+  </si>
+  <si>
+    <t>ClsWin</t>
+  </si>
+  <si>
+    <t>Pwd</t>
+  </si>
+  <si>
+    <t>PrtScn</t>
   </si>
 </sst>
 </file>
@@ -376,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -420,6 +432,45 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -438,6 +489,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -462,47 +516,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,7 +556,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F260F60A-DBEE-42CC-E5BD-D375680FC416}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F260F60A-DBEE-42CC-E5BD-D375680FC416}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -597,7 +612,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA941E0-F4D6-44EA-A8EB-038D50ADF789}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CAA941E0-F4D6-44EA-A8EB-038D50ADF789}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -708,6 +723,120 @@
         <a:xfrm>
           <a:off x="3441160" y="64851"/>
           <a:ext cx="502597" cy="496153"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>44584</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>32427</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>543127</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>578169</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4948946" y="32427"/>
+          <a:ext cx="498543" cy="545742"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>216633</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2922</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>403713</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190002</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4516490" y="611532"/>
+          <a:ext cx="187080" cy="187080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>213198</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>5591</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>401265</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>747</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5730276" y="614201"/>
+          <a:ext cx="188067" cy="185656"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1016,14 +1145,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4.85546875" customWidth="1"/>
     <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="4.85546875" customWidth="1"/>
+    <col min="9" max="11" width="9.140625" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
@@ -1031,73 +1162,83 @@
       <c r="F1" s="15"/>
       <c r="G1" s="16"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="32">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
         <v>7</v>
       </c>
-      <c r="B2" s="33">
+      <c r="B2" s="18">
         <v>8</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="19">
         <v>9</v>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="17">
         <v>7</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="18">
         <v>8</v>
       </c>
-      <c r="G2" s="34">
+      <c r="G2" s="19">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="19"/>
+      <c r="F3" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="45" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="18"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="31"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="37">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="22">
         <v>4</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="21">
         <v>5</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="20">
         <v>6</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="22">
         <v>4</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="21">
         <v>5</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="20">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -1105,17 +1246,17 @@
         <v>4</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="30" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
@@ -1123,51 +1264,51 @@
         <v>5</v>
       </c>
       <c r="C7" s="10"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="18"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="38">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="23">
         <v>1</v>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="24">
         <v>2</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="25">
         <v>3</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="23">
         <v>1</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="24">
         <v>2</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="25">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="8"/>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="13"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="21"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="34"/>
     </row>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
